--- a/data/native_non-native_historical.xlsx
+++ b/data/native_non-native_historical.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chris/claude-projects/worldcup2026-coachmchugh/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chris/claude-projects/worldcup2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4690D8-269D-D941-B6CB-A8F699455D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358EBE3A-7BBE-CB4E-BE50-31019763E974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20320" xr2:uid="{F4F4FD36-BF3F-8A48-AE70-B40A5136DB1E}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20320" activeTab="2" xr2:uid="{F4F4FD36-BF3F-8A48-AE70-B40A5136DB1E}"/>
   </bookViews>
   <sheets>
     <sheet name="historical_summary" sheetId="4" r:id="rId1"/>
@@ -21,11 +21,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2010-2022_team_coaches_records'!$A$1:$M$129</definedName>
-    <definedName name="_xlchart.v2.0" hidden="1">historical_summary!$A$50</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">historical_summary!$A$51</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">historical_summary!$B$49:$G$49</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">historical_summary!$B$50:$G$50</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">historical_summary!$B$51:$G$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="292">
   <si>
     <t>team</t>
   </si>
@@ -3915,11 +3910,11 @@
         <v>6</v>
       </c>
       <c r="F3" s="4">
-        <f>B3-D3</f>
+        <f t="shared" ref="F3:G6" si="0">B3-D3</f>
         <v>6</v>
       </c>
       <c r="G3" s="18">
-        <f>C3-E3</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -3944,11 +3939,11 @@
         <v>3</v>
       </c>
       <c r="F4" s="4">
-        <f>B4-D4</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G4" s="18">
-        <f>C4-E4</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -3973,11 +3968,11 @@
         <v>5</v>
       </c>
       <c r="F5" s="4">
-        <f>B5-D5</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="G5" s="18">
-        <f>C5-E5</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -4002,11 +3997,11 @@
         <v>6</v>
       </c>
       <c r="F6" s="11">
-        <f>B6-D6</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="G6" s="20">
-        <f>C6-E6</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -4020,19 +4015,19 @@
         <v>12</v>
       </c>
       <c r="D7" s="21">
-        <f t="shared" ref="D7" si="0">AVERAGE(D3:D6)</f>
+        <f t="shared" ref="D7" si="1">AVERAGE(D3:D6)</f>
         <v>15</v>
       </c>
       <c r="E7" s="24">
-        <f t="shared" ref="E7" si="1">AVERAGE(E3:E6)</f>
+        <f t="shared" ref="E7" si="2">AVERAGE(E3:E6)</f>
         <v>5</v>
       </c>
       <c r="F7" s="24">
-        <f t="shared" ref="F7" si="2">AVERAGE(F3:F6)</f>
+        <f t="shared" ref="F7" si="3">AVERAGE(F3:F6)</f>
         <v>5</v>
       </c>
       <c r="G7" s="22">
-        <f t="shared" ref="G7" si="3">AVERAGE(G3:G6)</f>
+        <f t="shared" ref="G7" si="4">AVERAGE(G3:G6)</f>
         <v>7</v>
       </c>
     </row>
@@ -4069,11 +4064,11 @@
         <v>2010</v>
       </c>
       <c r="B11" s="8">
-        <f>((D11*D3)+(F11*F3))/(D3+F3)</f>
+        <f t="shared" ref="B11:C14" si="5">((D11*D3)+(F11*F3))/(D3+F3)</f>
         <v>4.45</v>
       </c>
       <c r="C11" s="9">
-        <f>((E11*E3)+(G11*G3))/(E3+G3)</f>
+        <f t="shared" si="5"/>
         <v>3.5625</v>
       </c>
       <c r="D11" s="8">
@@ -4098,11 +4093,11 @@
         <v>2014</v>
       </c>
       <c r="B12" s="8">
-        <f>((D12*D4)+(F12*F4))/(D4+F4)</f>
+        <f t="shared" si="5"/>
         <v>4.666666666666667</v>
       </c>
       <c r="C12" s="9">
-        <f>((E12*E4)+(G12*G4))/(E4+G4)</f>
+        <f t="shared" si="5"/>
         <v>3.2968253968253967</v>
       </c>
       <c r="D12" s="8">
@@ -4127,11 +4122,11 @@
         <v>2018</v>
       </c>
       <c r="B13" s="8">
-        <f>((D13*D5)+(F13*F5))/(D5+F5)</f>
+        <f t="shared" si="5"/>
         <v>4.6842105263157894</v>
       </c>
       <c r="C13" s="9">
-        <f>((E13*E5)+(G13*G5))/(E5+G5)</f>
+        <f t="shared" si="5"/>
         <v>3.0512820512820511</v>
       </c>
       <c r="D13" s="8">
@@ -4156,11 +4151,11 @@
         <v>2022</v>
       </c>
       <c r="B14" s="25">
-        <f>((D14*D6)+(F14*F6))/(D6+F6)</f>
+        <f t="shared" si="5"/>
         <v>4.7391304347826084</v>
       </c>
       <c r="C14" s="12">
-        <f>((E14*E6)+(G14*G6))/(E6+G6)</f>
+        <f t="shared" si="5"/>
         <v>3.3888888888888888</v>
       </c>
       <c r="D14" s="25">
@@ -4182,27 +4177,27 @@
     </row>
     <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="26">
-        <f t="shared" ref="B15:G15" si="4">AVERAGE(B11:B14)</f>
+        <f t="shared" ref="B15:G15" si="6">AVERAGE(B11:B14)</f>
         <v>4.635001906941266</v>
       </c>
       <c r="C15" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.3248740842490845</v>
       </c>
       <c r="D15" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5.3175770308123242</v>
       </c>
       <c r="E15" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.55</v>
       </c>
       <c r="F15" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.4499999999999997</v>
       </c>
       <c r="G15" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.4756944444444442</v>
       </c>
     </row>
@@ -4792,11 +4787,11 @@
         <v>2014</v>
       </c>
       <c r="B37" s="8">
-        <f t="shared" ref="B37:B39" si="5">((D37*D4)+(F37*F4))/(D4+F4)</f>
+        <f t="shared" ref="B37:B39" si="7">((D37*D4)+(F37*F4))/(D4+F4)</f>
         <v>1.2222222222222223</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" ref="C37:C39" si="6">((E37*E4)+(G37*G4))/(E4+G4)</f>
+        <f t="shared" ref="C37:C39" si="8">((E37*E4)+(G37*G4))/(E4+G4)</f>
         <v>0.6428571428571429</v>
       </c>
       <c r="D37" s="8">
@@ -4808,7 +4803,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="F37" s="8">
-        <f t="shared" ref="F37:F38" si="7">((C29*1)+(D29*2)+(E29*3)+(F29*4)+(G29*5))/F4</f>
+        <f t="shared" ref="F37:F38" si="9">((C29*1)+(D29*2)+(E29*3)+(F29*4)+(G29*5))/F4</f>
         <v>0</v>
       </c>
       <c r="G37" s="9">
@@ -4821,27 +4816,27 @@
         <v>2018</v>
       </c>
       <c r="B38" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.263157894736842</v>
       </c>
       <c r="C38" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.53846153846153844</v>
       </c>
       <c r="D38" s="8">
-        <f t="shared" ref="D38:D39" si="8">((C22*1)+(D22*2)+(E22*3)+(F22*4)+(G22*5))/D5</f>
+        <f t="shared" ref="D38:D39" si="10">((C22*1)+(D22*2)+(E22*3)+(F22*4)+(G22*5))/D5</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="E38" s="9">
-        <f t="shared" ref="E38" si="9">((I22*1)+(J22*2)+(K22*3)+(L22*4)+(M22*5))/E5</f>
+        <f t="shared" ref="E38" si="11">((I22*1)+(J22*2)+(K22*3)+(L22*4)+(M22*5))/E5</f>
         <v>1.4</v>
       </c>
       <c r="F38" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="G38" s="9">
-        <f t="shared" ref="G38:G39" si="10">((I30*1)+(J30*2)+(K30*3)+(L30*4)+(M30*5))/G5</f>
+        <f t="shared" ref="G38:G39" si="12">((I30*1)+(J30*2)+(K30*3)+(L30*4)+(M30*5))/G5</f>
         <v>0</v>
       </c>
     </row>
@@ -4850,15 +4845,15 @@
         <v>2022</v>
       </c>
       <c r="B39" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.3043478260869565</v>
       </c>
       <c r="C39" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="D39" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1.7058823529411764</v>
       </c>
       <c r="E39" s="12">
@@ -4870,7 +4865,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="G39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -4913,19 +4908,19 @@
         <v>30</v>
       </c>
       <c r="D44" s="47">
-        <f t="shared" ref="C44:G44" si="11">(SUM(D20:D23)/SUM($D$3:$D$6))*100</f>
+        <f t="shared" ref="D44:G44" si="13">(SUM(D20:D23)/SUM($D$3:$D$6))*100</f>
         <v>18.333333333333332</v>
       </c>
       <c r="E44" s="47">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>11.666666666666666</v>
       </c>
       <c r="F44" s="47">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6.666666666666667</v>
       </c>
       <c r="G44" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6.666666666666667</v>
       </c>
     </row>
@@ -4938,23 +4933,23 @@
         <v>35</v>
       </c>
       <c r="C45" s="51">
-        <f t="shared" ref="C45:G45" si="12">(SUM(I20:I23)/SUM($E$3:$E$6))*100</f>
+        <f t="shared" ref="C45:G45" si="14">(SUM(I20:I23)/SUM($E$3:$E$6))*100</f>
         <v>50</v>
       </c>
       <c r="D45" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="E45" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="F45" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G45" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4993,23 +4988,23 @@
         <v>85</v>
       </c>
       <c r="C50" s="47">
-        <f t="shared" ref="C50:G50" si="13">(SUM(C28:C31)/SUM($F$3:$F$6))*100</f>
+        <f t="shared" ref="C50:G50" si="15">(SUM(C28:C31)/SUM($F$3:$F$6))*100</f>
         <v>10</v>
       </c>
       <c r="D50" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>5</v>
       </c>
       <c r="E50" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F50" s="47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G50" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5022,23 +5017,23 @@
         <v>85.714285714285708</v>
       </c>
       <c r="C51" s="51">
-        <f t="shared" ref="C51:G51" si="14">(SUM(I28:I31)/SUM($G$3:$G$6))*100</f>
+        <f t="shared" ref="C51:G51" si="16">(SUM(I28:I31)/SUM($G$3:$G$6))*100</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="D51" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>10.714285714285714</v>
       </c>
       <c r="E51" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F51" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G51" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -11055,6 +11050,15 @@
       <c r="B21" t="s">
         <v>20</v>
       </c>
+      <c r="C21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
+      </c>
       <c r="F21" t="str">
         <f>IF(COUNTIF(historically_strong_teams!$A$1:$A$25, A21)&gt;0,"Yes", "No")</f>
         <v>No</v>

--- a/data/native_non-native_historical.xlsx
+++ b/data/native_non-native_historical.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chris/claude-projects/worldcup2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358EBE3A-7BBE-CB4E-BE50-31019763E974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A07E064-0C75-2E48-805A-772421E2A7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20320" activeTab="2" xr2:uid="{F4F4FD36-BF3F-8A48-AE70-B40A5136DB1E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="27040" activeTab="2" xr2:uid="{F4F4FD36-BF3F-8A48-AE70-B40A5136DB1E}"/>
   </bookViews>
   <sheets>
     <sheet name="historical_summary" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="291">
   <si>
     <t>team</t>
   </si>
@@ -750,15 +750,6 @@
     <t>Bubista</t>
   </si>
   <si>
-    <t>Zlatko Daliƒá</t>
-  </si>
-  <si>
-    <t>Cura√ßao</t>
-  </si>
-  <si>
-    <t>Dick Advocaat</t>
-  </si>
-  <si>
     <t>Miroslav Koubek</t>
   </si>
   <si>
@@ -807,9 +798,6 @@
     <t>Graham Potter</t>
   </si>
   <si>
-    <t>Sami Trabelsi</t>
-  </si>
-  <si>
     <t>Vincenzo Montella</t>
   </si>
   <si>
@@ -919,6 +907,15 @@
   </si>
   <si>
     <t>Stages as %age - Scrubs</t>
+  </si>
+  <si>
+    <t>Fred Rutten</t>
+  </si>
+  <si>
+    <t>Mohamed Ouahbi</t>
+  </si>
+  <si>
+    <t>Curacao</t>
   </si>
 </sst>
 </file>
@@ -4203,7 +4200,7 @@
     </row>
     <row r="18" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -4211,40 +4208,40 @@
         <v>69</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="G19" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="H19" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="I19" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="J19" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="K19" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="L19" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="M19" s="7" t="s">
         <v>272</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -4469,7 +4466,7 @@
     </row>
     <row r="26" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
@@ -4477,40 +4474,40 @@
         <v>69</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="G27" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="H27" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="I27" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="J27" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="K27" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="L27" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="M27" s="7" t="s">
         <v>272</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
@@ -4727,7 +4724,7 @@
     </row>
     <row r="34" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -4738,19 +4735,19 @@
         <v>213</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>280</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -4871,25 +4868,25 @@
     </row>
     <row r="42" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="48"/>
       <c r="B43" s="10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>134</v>
@@ -4897,7 +4894,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="49" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B44" s="47">
         <f>(SUM(B20:B23)/SUM($D$3:$D$6))*100</f>
@@ -4926,7 +4923,7 @@
     </row>
     <row r="45" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B45" s="51">
         <f>(SUM(H20:H23)/SUM($E$3:$E$6))*100</f>
@@ -4955,25 +4952,25 @@
     </row>
     <row r="48" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="48"/>
       <c r="B49" s="10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>134</v>
@@ -4981,7 +4978,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="49" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B50" s="47">
         <f>(SUM(B28:B31)/SUM($F$3:$F$6))*100</f>
@@ -5010,7 +5007,7 @@
     </row>
     <row r="51" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="50" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B51" s="51">
         <f>(SUM(H28:H31)/SUM($G$3:$G$6))*100</f>
@@ -10841,7 +10838,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -10862,7 +10859,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>235</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
@@ -10877,13 +10874,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -10904,7 +10901,7 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -10925,7 +10922,7 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D15" t="s">
         <v>30</v>
@@ -10946,7 +10943,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -10967,7 +10964,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -10988,7 +10985,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -11030,7 +11027,7 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -11066,13 +11063,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D22" t="s">
         <v>30</v>
@@ -11093,7 +11090,7 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D23" t="s">
         <v>34</v>
@@ -11135,7 +11132,7 @@
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s">
         <v>129</v>
@@ -11171,13 +11168,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
@@ -11219,7 +11216,7 @@
         <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>289</v>
       </c>
       <c r="D29" t="s">
         <v>39</v>
@@ -11240,7 +11237,7 @@
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D30" t="s">
         <v>41</v>
@@ -11261,7 +11258,7 @@
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D31" t="s">
         <v>29</v>
@@ -11282,7 +11279,7 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D32" t="s">
         <v>45</v>
@@ -11303,7 +11300,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D33" t="s">
         <v>25</v>
@@ -11366,7 +11363,7 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D36" t="s">
         <v>51</v>
@@ -11429,7 +11426,7 @@
         <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D39" t="s">
         <v>56</v>
@@ -11450,7 +11447,7 @@
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -11492,7 +11489,7 @@
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D42" t="s">
         <v>51</v>
@@ -11513,7 +11510,7 @@
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -11555,7 +11552,7 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>254</v>
+        <v>150</v>
       </c>
       <c r="D45" t="s">
         <v>62</v>
@@ -11576,7 +11573,7 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
@@ -11805,10 +11802,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
